--- a/artfynd/A 26442-2026 artfynd.xlsx
+++ b/artfynd/A 26442-2026 artfynd.xlsx
@@ -1818,7 +1818,7 @@
         <v>136495630</v>
       </c>
       <c r="B12" t="n">
-        <v>93392</v>
+        <v>93395</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2388,7 +2388,7 @@
         <v>136495655</v>
       </c>
       <c r="B17" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 26442-2026 artfynd.xlsx
+++ b/artfynd/A 26442-2026 artfynd.xlsx
@@ -1818,7 +1818,7 @@
         <v>136495630</v>
       </c>
       <c r="B12" t="n">
-        <v>93395</v>
+        <v>93396</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2388,7 +2388,7 @@
         <v>136495655</v>
       </c>
       <c r="B17" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 26442-2026 artfynd.xlsx
+++ b/artfynd/A 26442-2026 artfynd.xlsx
@@ -1818,7 +1818,7 @@
         <v>136495630</v>
       </c>
       <c r="B12" t="n">
-        <v>93396</v>
+        <v>93401</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2388,7 +2388,7 @@
         <v>136495655</v>
       </c>
       <c r="B17" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 26442-2026 artfynd.xlsx
+++ b/artfynd/A 26442-2026 artfynd.xlsx
@@ -1818,7 +1818,7 @@
         <v>136495630</v>
       </c>
       <c r="B12" t="n">
-        <v>93401</v>
+        <v>93403</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2388,7 +2388,7 @@
         <v>136495655</v>
       </c>
       <c r="B17" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 26442-2026 artfynd.xlsx
+++ b/artfynd/A 26442-2026 artfynd.xlsx
@@ -1818,7 +1818,7 @@
         <v>136495630</v>
       </c>
       <c r="B12" t="n">
-        <v>93403</v>
+        <v>93405</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2388,7 +2388,7 @@
         <v>136495655</v>
       </c>
       <c r="B17" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 26442-2026 artfynd.xlsx
+++ b/artfynd/A 26442-2026 artfynd.xlsx
@@ -1818,7 +1818,7 @@
         <v>136495630</v>
       </c>
       <c r="B12" t="n">
-        <v>93405</v>
+        <v>93407</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2388,7 +2388,7 @@
         <v>136495655</v>
       </c>
       <c r="B17" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 26442-2026 artfynd.xlsx
+++ b/artfynd/A 26442-2026 artfynd.xlsx
@@ -1818,7 +1818,7 @@
         <v>136495630</v>
       </c>
       <c r="B12" t="n">
-        <v>93407</v>
+        <v>93408</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2388,7 +2388,7 @@
         <v>136495655</v>
       </c>
       <c r="B17" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 26442-2026 artfynd.xlsx
+++ b/artfynd/A 26442-2026 artfynd.xlsx
@@ -1818,7 +1818,7 @@
         <v>136495630</v>
       </c>
       <c r="B12" t="n">
-        <v>93408</v>
+        <v>93414</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2388,7 +2388,7 @@
         <v>136495655</v>
       </c>
       <c r="B17" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 26442-2026 artfynd.xlsx
+++ b/artfynd/A 26442-2026 artfynd.xlsx
@@ -1818,7 +1818,7 @@
         <v>136495630</v>
       </c>
       <c r="B12" t="n">
-        <v>93414</v>
+        <v>93418</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2388,7 +2388,7 @@
         <v>136495655</v>
       </c>
       <c r="B17" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
